--- a/artfynd/S 8060-2021 artfynd.xlsx
+++ b/artfynd/S 8060-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>65127921</v>
+        <v>137278907</v>
       </c>
       <c r="B8" t="n">
-        <v>109815</v>
+        <v>58036</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,40 +1381,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220204</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Klätta, lövskog, 350 m NV om Hagarna, Boh</t>
+          <t>Backetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>280632</v>
+        <v>280501</v>
       </c>
       <c r="R8" t="n">
-        <v>6521068</v>
+        <v>6521117</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,19 +1441,24 @@
           <t>Tanum</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Arkiv-OB-Tan-0727</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1998-07-16</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1998-07-16</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,31 +1473,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Evastina Blomgren</t>
+          <t>Matti Åhlund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kjell Emanuelsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Arkiv Floraväktarlokaler</t>
-        </is>
-      </c>
+          <t>Matti Åhlund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/65127921</t>
+          <t>https://artportalen.se/Sighting/137278907</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>90122063</v>
+        <v>137278926</v>
       </c>
       <c r="B9" t="n">
-        <v>109815</v>
+        <v>58182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,37 +1501,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220204</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>350 m NV om Hagarna, Klätta, Boh</t>
+          <t>Backetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>280637</v>
+        <v>280501</v>
       </c>
       <c r="R9" t="n">
-        <v>6521073</v>
+        <v>6521117</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,17 +1563,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1998-07-16</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1998-07-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Bohusläns flora - 2011.</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,40 +1589,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Evastina Blomgren</t>
+          <t>Matti Åhlund</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olof Holmstrand</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Bohusläns Flora 2011</t>
-        </is>
-      </c>
+          <t>Matti Åhlund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90122063</t>
+          <t>https://artportalen.se/Sighting/137278926</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105806142</v>
+        <v>65127921</v>
       </c>
       <c r="B10" t="n">
-        <v>110078</v>
+        <v>109815</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,16 +1621,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>220204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1629,19 +1639,22 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>TANUM: KLÄTTA, Boh</t>
+          <t>Klätta, lövskog, 350 m NV om Hagarna, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>280652</v>
+        <v>280632</v>
       </c>
       <c r="R10" t="n">
-        <v>6520997</v>
+        <v>6521068</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1663,19 +1676,19 @@
           <t>Tanum</t>
         </is>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Arkiv-OB-Tan-0727</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1920-01-01</t>
+          <t>1998-07-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1945-12-31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
+          <t>1998-07-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,31 +1703,31 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Evastina Blomgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Mora Aronsson</t>
+          <t>Kjell Emanuelsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>Göteborg och Bohusläns flora 1945</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105806142</t>
+          <t>https://artportalen.se/Sighting/65127921</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105806238</v>
+        <v>90122063</v>
       </c>
       <c r="B11" t="n">
-        <v>102560</v>
+        <v>109815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1722,16 +1735,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222133</v>
+        <v>220204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1742,17 +1755,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>TANUM: KLÄTTA, Boh</t>
+          <t>350 m NV om Hagarna, Klätta, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>280652</v>
+        <v>280637</v>
       </c>
       <c r="R11" t="n">
-        <v>6520997</v>
+        <v>6521073</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,17 +1789,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1920-01-01</t>
+          <t>1998-07-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1945-12-31</t>
+          <t>1998-07-16</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
+          <t>Bohusläns flora - 2011.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,57 +1810,62 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Evastina Blomgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Mora Aronsson</t>
+          <t>Olof Holmstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Göteborg och Bohusläns flora 1945</t>
+          <t>Bohusläns Flora 2011</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105806238</t>
+          <t>https://artportalen.se/Sighting/90122063</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105806176</v>
+        <v>105806142</v>
       </c>
       <c r="B12" t="n">
-        <v>99707</v>
+        <v>110078</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222237</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödsäv</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Blysmus rufus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Huds.) Link</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1927,38 +1945,38 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105806176</t>
+          <t>https://artportalen.se/Sighting/105806142</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105806242</v>
+        <v>105806238</v>
       </c>
       <c r="B13" t="n">
-        <v>101326</v>
+        <v>102560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>222133</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2038,38 +2056,38 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105806242</t>
+          <t>https://artportalen.se/Sighting/105806238</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105806143</v>
+        <v>105806176</v>
       </c>
       <c r="B14" t="n">
-        <v>106699</v>
+        <v>99707</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223438</v>
+        <v>222237</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bolmört</t>
+          <t>Rödsäv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hyoscyamus niger</t>
+          <t>Blysmus rufus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Huds.) Link</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2148,6 +2166,228 @@
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105806176</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>105806242</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>TANUM: KLÄTTA, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>280652</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6520997</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>1920-01-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1945-12-31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Via Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Göteborg och Bohusläns flora 1945</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105806242</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>105806143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106699</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>223438</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bolmört</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hyoscyamus niger</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>TANUM: KLÄTTA, Boh</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>280652</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6520997</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>1920-01-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1945-12-31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Göteborg och Bohusläns flora 1945</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/105806143</t>
         </is>
@@ -2168,6 +2408,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 8060-2021 artfynd.xlsx
+++ b/artfynd/S 8060-2021 artfynd.xlsx
@@ -1373,7 +1373,7 @@
         <v>137278907</v>
       </c>
       <c r="B8" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>137278926</v>
       </c>
       <c r="B9" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 8060-2021 artfynd.xlsx
+++ b/artfynd/S 8060-2021 artfynd.xlsx
@@ -1373,7 +1373,7 @@
         <v>137278907</v>
       </c>
       <c r="B8" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>137278926</v>
       </c>
       <c r="B9" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 8060-2021 artfynd.xlsx
+++ b/artfynd/S 8060-2021 artfynd.xlsx
@@ -1373,7 +1373,7 @@
         <v>137278907</v>
       </c>
       <c r="B8" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>137278926</v>
       </c>
       <c r="B9" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 8060-2021 artfynd.xlsx
+++ b/artfynd/S 8060-2021 artfynd.xlsx
@@ -1373,7 +1373,7 @@
         <v>137278907</v>
       </c>
       <c r="B8" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>137278926</v>
       </c>
       <c r="B9" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
